--- a/server/excel/release/system-prompt-localization.xlsx
+++ b/server/excel/release/system-prompt-localization.xlsx
@@ -2310,13 +2310,13 @@
     <t xml:space="preserve">速度提升:</t>
   </si>
   <si>
-    <t xml:space="preserve">Tốc độ tăng lên:</t>
+    <t xml:space="preserve">Tốc độ:</t>
   </si>
   <si>
     <t xml:space="preserve">攻血成长:</t>
   </si>
   <si>
-    <t xml:space="preserve">Công máu trưởng thành:</t>
+    <t xml:space="preserve">Công/máu:</t>
   </si>
   <si>
     <t xml:space="preserve">攻击成长:</t>
